--- a/Achievement Tracker.xlsx
+++ b/Achievement Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan Leich\Documents\GitHub\Improved-Unlockables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B263D69B-5B5D-48AE-9D37-93EC5219B5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696F08A2-B053-4E6A-83E9-05A76B2B29A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30E7719E-5702-483A-BB06-339396A797C9}"/>
   </bookViews>
@@ -782,15 +782,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -798,6 +789,40 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -835,29 +860,13 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -869,7 +878,7 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -877,15 +886,6 @@
           <color rgb="FF8EA9DB"/>
         </left>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2434,12 +2434,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF663D5E-0759-4E4B-87CC-19B1AB6B6A75}" name="Table15" displayName="Table15" ref="A1:C62" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF663D5E-0759-4E4B-87CC-19B1AB6B6A75}" name="Table15" displayName="Table15" ref="A1:C62" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="6" tableBorderDxfId="7">
   <autoFilter ref="A1:C61" xr:uid="{FF66C5D9-ED34-8F49-9B1C-C38D8DEA47EB}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{141D096E-F14D-4E60-ABA6-8D3261881413}" name="Achievement Icon" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{C321B8E8-0265-46CB-984A-86660BB68D40}" name="Achievement Name" totalsRowLabel="Total" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{4A463D9A-9910-4C6B-83BA-16664CDACDE1}" name="Unlocked" totalsRowFunction="count" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{141D096E-F14D-4E60-ABA6-8D3261881413}" name="Achievement Icon" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{C321B8E8-0265-46CB-984A-86660BB68D40}" name="Achievement Name" totalsRowLabel="Total" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{4A463D9A-9910-4C6B-83BA-16664CDACDE1}" name="Unlocked" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2755,7 +2755,7 @@
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>64</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3" t="s">
         <v>0</v>
